--- a/Result/profitability/2007.xlsx
+++ b/Result/profitability/2007.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.465</v>
+        <v>-0.44125</v>
       </c>
       <c r="N2" t="n">
-        <v>-8.90375</v>
+        <v>-8.85125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.37375</v>
+        <v>-0.35625</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.07375</v>
+        <v>-6.466249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3337499999999999</v>
+        <v>-0.3325</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.65</v>
+        <v>-5.6625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.35</v>
+        <v>-0.3212499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.567500000000001</v>
+        <v>-6.8975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.29125</v>
+        <v>-0.26625</v>
       </c>
       <c r="N6" t="n">
-        <v>-8.0075</v>
+        <v>-7.4575</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.255</v>
+        <v>-0.215</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.05875</v>
+        <v>-4.0075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.16375</v>
+        <v>-0.15375</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.58625</v>
+        <v>-2.135</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.03749999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5337500000000002</v>
+        <v>-0.5337499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01875</v>
+        <v>-0.01874999999999998</v>
       </c>
       <c r="N10" t="n">
         <v>-0.1075000000000002</v>
@@ -1772,7 +1772,7 @@
         <v>0.28</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.004999999999999998</v>
+        <v>-0.004999999999999984</v>
       </c>
       <c r="N11" t="n">
         <v>-0.08750000000000013</v>
@@ -1899,7 +1899,7 @@
         <v>0.02</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02125</v>
+        <v>0.02125000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>0.5337499999999999</v>
@@ -2026,7 +2026,7 @@
         <v>0.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0975</v>
+        <v>0.09750000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>3.5925</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1213</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1272</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-58</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.53%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-79</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-182</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-195</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.51625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-10.18</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1777777777777778</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4287410926365797</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3833333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5270403146509341</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
